--- a/output/2022/sector_totals_v2.5_year2022.xlsx
+++ b/output/2022/sector_totals_v2.5_year2022.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1591.300216769622</v>
+        <v>1677.263061860291</v>
       </c>
       <c r="C3" t="n">
-        <v>106.0011106572547</v>
+        <v>97.70465611673924</v>
       </c>
       <c r="D3" t="n">
-        <v>634.1990528221818</v>
+        <v>663.4238963223078</v>
       </c>
       <c r="E3" t="n">
-        <v>1973.068750723196</v>
+        <v>1866.110276606194</v>
       </c>
       <c r="F3" t="n">
-        <v>168.2341515367415</v>
+        <v>164.9621032792324</v>
       </c>
       <c r="G3" t="n">
-        <v>79.15529043845791</v>
+        <v>73.32404832630318</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5845.323501065241</v>
+        <v>5931.286346155912</v>
       </c>
       <c r="C16" t="n">
-        <v>965.8202541602368</v>
+        <v>957.5237996197213</v>
       </c>
       <c r="D16" t="n">
-        <v>4326.956783750606</v>
+        <v>4356.181627250731</v>
       </c>
       <c r="E16" t="n">
-        <v>8471.474303077583</v>
+        <v>8364.515828960579</v>
       </c>
       <c r="F16" t="n">
-        <v>1658.97799000598</v>
+        <v>1655.705941748472</v>
       </c>
       <c r="G16" t="n">
-        <v>109.1565079758694</v>
+        <v>103.3252658637146</v>
       </c>
     </row>
   </sheetData>
